--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroup.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroup.xlsx
@@ -514,47 +514,47 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E3" s="4">
         <v>254000000000002</v>
       </c>
       <c r="G3" s="7" t="str">
         <f t="shared" ref="G3:G11" si="0">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroup_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, '", B3, "'::varchar, '", C3, "'::varchar);")</f>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Budget'::varchar, 'fas fa-shopping-basket'::varchar);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Admin'::varchar, 'fas fa-user'::varchar);</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E4" s="4">
         <v>254000000000003</v>
       </c>
       <c r="G4" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Human Resource'::varchar, 'fas fa-users'::varchar);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Register'::varchar, 'fas fa-registered'::varchar);</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4">
         <v>254000000000004</v>
       </c>
       <c r="G5" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Finance'::varchar, 'fas fa-credit-card'::varchar);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Budget'::varchar, 'fas fa-shopping-basket'::varchar);</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
@@ -574,77 +574,77 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7" s="4">
         <v>254000000000006</v>
       </c>
       <c r="G7" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Process'::varchar, 'fas fa-hourglass-start'::varchar);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Finance'::varchar, 'fas fa-credit-card'::varchar);</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E8" s="4">
         <v>254000000000007</v>
       </c>
       <c r="G8" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Purchase'::varchar, 'fas fa-cart-arrow-down'::varchar);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Human Resource'::varchar, 'fas fa-users'::varchar);</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" s="4">
         <v>254000000000008</v>
       </c>
       <c r="G9" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Inventory'::varchar, 'fas fa-warehouse'::varchar);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Process'::varchar, 'fas fa-hourglass-start'::varchar);</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="4">
         <v>254000000000009</v>
       </c>
       <c r="G10" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Register'::varchar, 'fas fa-registered'::varchar);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Inventory'::varchar, 'fas fa-warehouse'::varchar);</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E11" s="4">
         <v>254000000000010</v>
       </c>
       <c r="G11" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Admin'::varchar, 'fas fa-user'::varchar);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Purchase'::varchar, 'fas fa-cart-arrow-down'::varchar);</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroup.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroup.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" iterateDelta="1E-4"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -34,9 +34,6 @@
     <t>Sales</t>
   </si>
   <si>
-    <t>Process</t>
-  </si>
-  <si>
     <t>Purchase</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
   </si>
   <si>
     <t>fas fa-user</t>
+  </si>
+  <si>
+    <t>Advance &amp; Trip</t>
   </si>
 </sst>
 </file>
@@ -488,10 +488,10 @@
   <sheetData>
     <row r="1" spans="2:7" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>0</v>
@@ -502,7 +502,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4">
         <v>254000000000001</v>
@@ -514,10 +514,10 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="4">
         <v>254000000000002</v>
@@ -529,10 +529,10 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" s="4">
         <v>254000000000003</v>
@@ -547,7 +547,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="4">
         <v>254000000000004</v>
@@ -562,7 +562,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" s="4">
         <v>254000000000005</v>
@@ -577,7 +577,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4">
         <v>254000000000006</v>
@@ -592,7 +592,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="4">
         <v>254000000000007</v>
@@ -604,25 +604,25 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="4">
         <v>254000000000008</v>
       </c>
       <c r="G9" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Process'::varchar, 'fas fa-hourglass-start'::varchar);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Advance &amp; Trip'::varchar, 'fas fa-hourglass-start'::varchar);</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" s="4">
         <v>254000000000009</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" s="4">
         <v>254000000000010</v>

--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroup.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroup.xlsx
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G11"/>
+  <dimension ref="B1:I11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -486,7 +486,7 @@
     <col min="7" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B1" s="6" t="s">
         <v>10</v>
       </c>
@@ -497,7 +497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
@@ -511,8 +511,25 @@
         <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroup_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, '", B2, "'::varchar, '", C2, "'::varchar);")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Home'::varchar, 'fas fa-home'::varchar);</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="I2" s="1" t="str">
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'name', ", IF(EXACT($B2, ""), "null", CONCATENATE("'", SUBSTITUTE($B2, "'", "\'"), "'")), "::varchar,",
+"'iconSource', ", IF(EXACT($C2, ""), "null", CONCATENATE("'", SUBSTITUTE($C2, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Home'::varchar,'iconSource', 'fas fa-home'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
@@ -526,8 +543,25 @@
         <f t="shared" ref="G3:G11" si="0">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroup_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, '", B3, "'::varchar, '", C3, "'::varchar);")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Admin'::varchar, 'fas fa-user'::varchar);</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="I3" s="1" t="str">
+        <f t="shared" ref="I3:I11" si="1">CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'name', ", IF(EXACT($B3, ""), "null", CONCATENATE("'", SUBSTITUTE($B3, "'", "\'"), "'")), "::varchar,",
+"'iconSource', ", IF(EXACT($C3, ""), "null", CONCATENATE("'", SUBSTITUTE($C3, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Admin'::varchar,'iconSource', 'fas fa-user'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
@@ -541,8 +575,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Register'::varchar, 'fas fa-registered'::varchar);</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="I4" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Register'::varchar,'iconSource', 'fas fa-registered'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -556,8 +594,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Budget'::varchar, 'fas fa-shopping-basket'::varchar);</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="I5" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Budget'::varchar,'iconSource', 'fas fa-shopping-basket'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
@@ -571,8 +613,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Sales'::varchar, 'fas fa-chart-line'::varchar);</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="I6" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Sales'::varchar,'iconSource', 'fas fa-chart-line'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
@@ -586,8 +632,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Finance'::varchar, 'fas fa-credit-card'::varchar);</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="I7" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Finance'::varchar,'iconSource', 'fas fa-credit-card'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
         <v>3</v>
       </c>
@@ -601,8 +651,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Human Resource'::varchar, 'fas fa-users'::varchar);</v>
       </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="I8" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Human Resource'::varchar,'iconSource', 'fas fa-users'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
@@ -616,8 +670,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Advance &amp; Trip'::varchar, 'fas fa-hourglass-start'::varchar);</v>
       </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="I9" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Advance &amp; Trip'::varchar,'iconSource', 'fas fa-hourglass-start'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
@@ -631,8 +689,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Inventory'::varchar, 'fas fa-warehouse'::varchar);</v>
       </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="I10" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Inventory'::varchar,'iconSource', 'fas fa-warehouse'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
@@ -645,6 +707,10 @@
       <c r="G11" s="7" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroup_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Purchase'::varchar, 'fas fa-cart-arrow-down'::varchar);</v>
+      </c>
+      <c r="I11" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Purchase'::varchar,'iconSource', 'fas fa-cart-arrow-down'::varchar)))::varchar;</v>
       </c>
     </row>
   </sheetData>
